--- a/Methanol/Patagonien_Methanol_4_Bio_H2_Brownfield/Datenbank.xlsx
+++ b/Methanol/Patagonien_Methanol_4_Bio_H2_Brownfield/Datenbank.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Patagonien_Methanol_4_Bio_H2_Brownfield\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC25742A-4D47-4CB8-B310-352DBB6B9EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54712CCE-05F3-443B-A59A-BC163F546BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-4455" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-6885" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
     <sheet name="Ergebnisse" sheetId="5" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="9.8999999999999999E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="394">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1358,6 +1358,12 @@
   </si>
   <si>
     <t>kg</t>
+  </si>
+  <si>
+    <t>Landesspezifischer Zinssatz</t>
+  </si>
+  <si>
+    <t>wacc_change</t>
   </si>
 </sst>
 </file>
@@ -1984,23 +1990,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G77"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G78"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="25" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="25" customWidth="1"/>
+    <col min="3" max="3" width="36.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" style="30" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" customWidth="1"/>
+    <col min="9" max="9" width="13.90625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="22" t="s">
         <v>69</v>
       </c>
@@ -2021,7 +2027,7 @@
       </c>
       <c r="G1" s="25"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="53" t="s">
         <v>70</v>
       </c>
@@ -2041,7 +2047,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="54"/>
       <c r="B3" s="61"/>
       <c r="C3" t="s">
@@ -2057,7 +2063,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="54"/>
       <c r="B4" s="61"/>
       <c r="C4" t="s">
@@ -2073,7 +2079,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="54"/>
       <c r="B5" s="61"/>
       <c r="C5" t="s">
@@ -2089,7 +2095,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="54"/>
       <c r="B6" s="61"/>
       <c r="C6" t="s">
@@ -2105,7 +2111,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="54"/>
       <c r="B7" s="61"/>
       <c r="C7" t="s">
@@ -2121,7 +2127,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="54"/>
       <c r="B8" s="64" t="s">
         <v>227</v>
@@ -2139,7 +2145,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="54"/>
       <c r="B9" s="61"/>
       <c r="C9" t="s">
@@ -2155,7 +2161,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="54"/>
       <c r="B10" s="61"/>
       <c r="C10" t="s">
@@ -2171,7 +2177,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="54"/>
       <c r="B11" s="61"/>
       <c r="C11" t="s">
@@ -2187,7 +2193,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="54"/>
       <c r="B12" s="61"/>
       <c r="C12" t="s">
@@ -2203,7 +2209,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="54"/>
       <c r="B13" s="61"/>
       <c r="C13" t="s">
@@ -2219,7 +2225,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="54"/>
       <c r="B14" s="61"/>
       <c r="C14" t="s">
@@ -2235,7 +2241,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="54"/>
       <c r="B15" s="65"/>
       <c r="C15" s="34" t="s">
@@ -2251,7 +2257,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="54"/>
       <c r="B16" s="64" t="s">
         <v>269</v>
@@ -2269,7 +2275,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="54"/>
       <c r="B17" s="61"/>
       <c r="C17" t="s">
@@ -2285,7 +2291,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="54"/>
       <c r="B18" s="61"/>
       <c r="C18" t="s">
@@ -2301,7 +2307,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="54"/>
       <c r="B19" s="61"/>
       <c r="C19" t="s">
@@ -2317,7 +2323,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="54"/>
       <c r="B20" s="61"/>
       <c r="C20" t="s">
@@ -2333,7 +2339,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="54"/>
       <c r="B21" s="65"/>
       <c r="C21" s="34" t="s">
@@ -2349,7 +2355,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="54"/>
       <c r="B22" s="57" t="s">
         <v>336</v>
@@ -2367,7 +2373,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="54"/>
       <c r="B23" s="57"/>
       <c r="C23" t="s">
@@ -2383,7 +2389,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="54"/>
       <c r="B24" s="57"/>
       <c r="C24" t="s">
@@ -2399,7 +2405,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="54"/>
       <c r="B25" s="57"/>
       <c r="C25" t="s">
@@ -2415,7 +2421,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="54"/>
       <c r="B26" s="57"/>
       <c r="C26" t="s">
@@ -2431,7 +2437,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="54"/>
       <c r="B27" s="57"/>
       <c r="C27" t="s">
@@ -2447,7 +2453,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="54"/>
       <c r="B28" s="57"/>
       <c r="C28" t="s">
@@ -2463,7 +2469,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="54"/>
       <c r="B29" s="57"/>
       <c r="C29" t="s">
@@ -2479,7 +2485,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="54"/>
       <c r="B30" s="57"/>
       <c r="C30" t="s">
@@ -2495,7 +2501,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="53" t="s">
         <v>71</v>
       </c>
@@ -2515,7 +2521,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="54"/>
       <c r="B32" s="57"/>
       <c r="C32" t="s">
@@ -2531,7 +2537,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="54"/>
       <c r="B33" s="57"/>
       <c r="C33" t="s">
@@ -2547,7 +2553,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="54"/>
       <c r="B34" s="57"/>
       <c r="C34" t="s">
@@ -2563,7 +2569,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="54"/>
       <c r="B35" s="57"/>
       <c r="C35" t="s">
@@ -2579,7 +2585,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="54"/>
       <c r="B36" s="57"/>
       <c r="C36" t="s">
@@ -2595,7 +2601,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="54"/>
       <c r="B37" s="57"/>
       <c r="C37" t="s">
@@ -2611,7 +2617,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="54"/>
       <c r="B38" s="58"/>
       <c r="C38" s="34" t="s">
@@ -2627,7 +2633,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="54"/>
       <c r="B39" s="59" t="s">
         <v>311</v>
@@ -2645,7 +2651,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="54"/>
       <c r="B40" s="57"/>
       <c r="C40" t="s">
@@ -2661,7 +2667,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="54"/>
       <c r="B41" s="57"/>
       <c r="C41" t="s">
@@ -2677,7 +2683,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="54"/>
       <c r="B42" s="57"/>
       <c r="C42" t="s">
@@ -2693,7 +2699,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="54"/>
       <c r="B43" s="57"/>
       <c r="C43" t="s">
@@ -2709,7 +2715,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="54"/>
       <c r="B44" s="57"/>
       <c r="C44" t="s">
@@ -2725,7 +2731,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="54"/>
       <c r="B45" s="57"/>
       <c r="C45" t="s">
@@ -2741,7 +2747,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="54"/>
       <c r="B46" s="57"/>
       <c r="C46" s="34" t="s">
@@ -2757,7 +2763,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="54"/>
       <c r="B47" s="59" t="s">
         <v>201</v>
@@ -2775,7 +2781,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="54"/>
       <c r="B48" s="61"/>
       <c r="C48" t="s">
@@ -2792,7 +2798,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="54"/>
       <c r="B49" s="61"/>
       <c r="C49" t="s">
@@ -2808,7 +2814,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="54"/>
       <c r="B50" s="61"/>
       <c r="C50" t="s">
@@ -2824,7 +2830,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="54"/>
       <c r="B51" s="61"/>
       <c r="C51" t="s">
@@ -2840,7 +2846,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="54"/>
       <c r="B52" s="61"/>
       <c r="C52" t="s">
@@ -2856,7 +2862,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="54"/>
       <c r="B53" s="61"/>
       <c r="C53" t="s">
@@ -2872,7 +2878,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="54"/>
       <c r="B54" s="61"/>
       <c r="C54" t="s">
@@ -2888,7 +2894,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="54"/>
       <c r="B55" s="61"/>
       <c r="C55" t="s">
@@ -2904,7 +2910,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="55"/>
       <c r="B56" s="62"/>
       <c r="C56" s="39" t="s">
@@ -2920,7 +2926,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="53" t="s">
         <v>72</v>
       </c>
@@ -2940,7 +2946,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="54"/>
       <c r="B58" s="44" t="s">
         <v>376</v>
@@ -2958,7 +2964,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="54"/>
       <c r="B59" s="47" t="s">
         <v>337</v>
@@ -2976,7 +2982,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="54"/>
       <c r="B60" s="59" t="s">
         <v>4</v>
@@ -2994,7 +3000,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="54"/>
       <c r="B61" s="57"/>
       <c r="C61" t="s">
@@ -3010,7 +3016,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="54"/>
       <c r="B62" s="57"/>
       <c r="C62" t="s">
@@ -3026,7 +3032,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="54"/>
       <c r="B63" s="57"/>
       <c r="C63" t="s">
@@ -3042,7 +3048,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="54"/>
       <c r="B64" s="57"/>
       <c r="C64" t="s">
@@ -3058,7 +3064,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="54"/>
       <c r="B65" s="57"/>
       <c r="C65" t="s">
@@ -3074,7 +3080,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="54"/>
       <c r="B66" s="58"/>
       <c r="C66" s="34" t="s">
@@ -3090,7 +3096,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="54"/>
       <c r="B67" s="59" t="s">
         <v>5</v>
@@ -3108,7 +3114,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="54"/>
       <c r="B68" s="57"/>
       <c r="C68" t="s">
@@ -3124,7 +3130,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="54"/>
       <c r="B69" s="57"/>
       <c r="C69" t="s">
@@ -3140,7 +3146,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="54"/>
       <c r="B70" s="57"/>
       <c r="C70" t="s">
@@ -3156,7 +3162,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="54"/>
       <c r="B71" s="57"/>
       <c r="C71" t="s">
@@ -3172,7 +3178,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="54"/>
       <c r="B72" s="57"/>
       <c r="C72" t="s">
@@ -3188,7 +3194,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="55"/>
       <c r="B73" s="60"/>
       <c r="C73" s="39" t="s">
@@ -3204,7 +3210,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="53" t="s">
         <v>76</v>
       </c>
@@ -3224,7 +3230,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="54"/>
       <c r="B75" s="25" t="s">
         <v>295</v>
@@ -3242,7 +3248,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="54"/>
       <c r="B76" s="52" t="s">
         <v>79</v>
@@ -3260,7 +3266,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="55"/>
       <c r="B77" s="23" t="s">
         <v>258</v>
@@ -3276,6 +3282,26 @@
       </c>
       <c r="F77" s="39" t="s">
         <v>271</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" t="s">
+        <v>392</v>
+      </c>
+      <c r="D78" t="s">
+        <v>393</v>
+      </c>
+      <c r="E78" s="30">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="F78" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3303,18 +3329,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
   <dimension ref="A1:F149"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.77734375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="37.5546875" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="5"/>
+    <col min="1" max="1" width="14.54296875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.54296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.81640625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="46.08984375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="37.54296875" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="11.54296875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -3334,7 +3360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="67" t="s">
         <v>70</v>
       </c>
@@ -3352,7 +3378,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="68"/>
       <c r="B3" s="66"/>
       <c r="C3" s="5" t="s">
@@ -3366,7 +3392,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="68"/>
       <c r="B4" s="66"/>
       <c r="C4" s="5" t="s">
@@ -3380,7 +3406,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="68"/>
       <c r="B5" s="66"/>
       <c r="C5" s="5" t="s">
@@ -3394,7 +3420,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="68"/>
       <c r="B6" s="66"/>
       <c r="C6" s="5" t="s">
@@ -3408,7 +3434,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="68"/>
       <c r="B7" s="66"/>
       <c r="C7" s="5" t="s">
@@ -3422,7 +3448,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="68"/>
       <c r="B8" s="66"/>
       <c r="C8" s="5" t="s">
@@ -3436,7 +3462,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="68"/>
       <c r="B9" s="66"/>
       <c r="C9" s="5" t="s">
@@ -3450,7 +3476,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="68"/>
       <c r="B10" s="66"/>
       <c r="C10" s="5" t="s">
@@ -3464,12 +3490,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="68"/>
       <c r="B11" s="66"/>
       <c r="E11" s="10"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="68"/>
       <c r="B12" s="70" t="s">
         <v>227</v>
@@ -3485,7 +3511,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="68"/>
       <c r="B13" s="66"/>
       <c r="C13" s="5" t="s">
@@ -3499,7 +3525,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="68"/>
       <c r="B14" s="66"/>
       <c r="C14" s="5" t="s">
@@ -3513,7 +3539,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="68"/>
       <c r="B15" s="66"/>
       <c r="C15" s="5" t="s">
@@ -3527,7 +3553,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="68"/>
       <c r="B16" s="66"/>
       <c r="C16" s="5" t="s">
@@ -3541,7 +3567,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="68"/>
       <c r="B17" s="66"/>
       <c r="C17" s="5" t="s">
@@ -3555,7 +3581,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="68"/>
       <c r="B18" s="66"/>
       <c r="C18" s="5" t="s">
@@ -3569,7 +3595,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="68"/>
       <c r="B19" s="66"/>
       <c r="C19" s="5" t="s">
@@ -3583,7 +3609,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="68"/>
       <c r="B20" s="66"/>
       <c r="C20" s="5" t="s">
@@ -3597,7 +3623,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="68"/>
       <c r="B21" s="66"/>
       <c r="C21" s="5" t="s">
@@ -3611,7 +3637,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="68"/>
       <c r="B22" s="71"/>
       <c r="C22" s="14"/>
@@ -3619,7 +3645,7 @@
       <c r="E22" s="15"/>
       <c r="F22" s="14"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="68"/>
       <c r="B23" s="70" t="s">
         <v>269</v>
@@ -3635,7 +3661,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="68"/>
       <c r="B24" s="66"/>
       <c r="C24" s="5" t="s">
@@ -3649,7 +3675,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="68"/>
       <c r="B25" s="66"/>
       <c r="C25" s="5" t="s">
@@ -3663,7 +3689,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="68"/>
       <c r="B26" s="66"/>
       <c r="C26" s="5" t="s">
@@ -3677,7 +3703,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="68"/>
       <c r="B27" s="66"/>
       <c r="C27" s="5" t="s">
@@ -3691,7 +3717,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="68"/>
       <c r="B28" s="66"/>
       <c r="C28" s="5" t="s">
@@ -3705,7 +3731,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="68"/>
       <c r="B29" s="66"/>
       <c r="C29" s="5" t="s">
@@ -3719,7 +3745,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="68"/>
       <c r="B30" s="66"/>
       <c r="C30" s="5" t="s">
@@ -3733,7 +3759,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="68"/>
       <c r="B31" s="66"/>
       <c r="C31" s="5" t="s">
@@ -3747,7 +3773,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="68"/>
       <c r="B32" s="71"/>
       <c r="C32" s="14"/>
@@ -3755,7 +3781,7 @@
       <c r="E32" s="15"/>
       <c r="F32" s="14"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="68"/>
       <c r="B33" s="72" t="s">
         <v>354</v>
@@ -3771,7 +3797,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="68"/>
       <c r="B34" s="72"/>
       <c r="C34" s="5" t="s">
@@ -3785,7 +3811,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="68"/>
       <c r="B35" s="72"/>
       <c r="C35" s="5" t="s">
@@ -3799,7 +3825,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="68"/>
       <c r="B36" s="72"/>
       <c r="C36" s="5" t="s">
@@ -3813,7 +3839,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="68"/>
       <c r="B37" s="72"/>
       <c r="C37" s="5" t="s">
@@ -3827,7 +3853,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="68"/>
       <c r="B38" s="72"/>
       <c r="C38" s="5" t="s">
@@ -3841,7 +3867,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="68"/>
       <c r="B39" s="72"/>
       <c r="C39" s="5" t="s">
@@ -3855,7 +3881,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="68"/>
       <c r="B40" s="72"/>
       <c r="C40" s="5" t="s">
@@ -3869,7 +3895,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="68"/>
       <c r="B41" s="72"/>
       <c r="C41" s="5" t="s">
@@ -3883,7 +3909,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="68"/>
       <c r="B42" s="72"/>
       <c r="C42" s="5" t="s">
@@ -3897,7 +3923,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="68"/>
       <c r="B43" s="72"/>
       <c r="C43" s="5" t="s">
@@ -3911,7 +3937,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="68"/>
       <c r="B44" s="72"/>
       <c r="C44" s="5" t="s">
@@ -3925,12 +3951,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="68"/>
       <c r="B45" s="72"/>
       <c r="E45" s="10"/>
     </row>
-    <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="67" t="s">
         <v>71</v>
       </c>
@@ -3948,7 +3974,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="68"/>
       <c r="B47" s="72"/>
       <c r="C47" s="5" t="s">
@@ -3962,7 +3988,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="68"/>
       <c r="B48" s="72"/>
       <c r="C48" s="5" t="s">
@@ -3976,7 +4002,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="68"/>
       <c r="B49" s="72"/>
       <c r="C49" s="5" t="s">
@@ -3990,7 +4016,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="68"/>
       <c r="B50" s="72"/>
       <c r="C50" s="5" t="s">
@@ -4004,7 +4030,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="68"/>
       <c r="B51" s="72"/>
       <c r="C51" s="5" t="s">
@@ -4018,7 +4044,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="68"/>
       <c r="B52" s="72"/>
       <c r="C52" s="5" t="s">
@@ -4032,7 +4058,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="68"/>
       <c r="B53" s="72"/>
       <c r="C53" s="5" t="s">
@@ -4046,7 +4072,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="68"/>
       <c r="B54" s="72"/>
       <c r="C54" s="5" t="s">
@@ -4060,7 +4086,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="68"/>
       <c r="B55" s="77"/>
       <c r="C55" s="14"/>
@@ -4068,7 +4094,7 @@
       <c r="E55" s="15"/>
       <c r="F55" s="14"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="68"/>
       <c r="B56" s="72" t="s">
         <v>311</v>
@@ -4084,7 +4110,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="68"/>
       <c r="B57" s="72"/>
       <c r="C57" s="5" t="s">
@@ -4098,7 +4124,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="68"/>
       <c r="B58" s="72"/>
       <c r="C58" s="5" t="s">
@@ -4112,7 +4138,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="68"/>
       <c r="B59" s="72"/>
       <c r="C59" s="5" t="s">
@@ -4126,7 +4152,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="68"/>
       <c r="B60" s="72"/>
       <c r="C60" s="5" t="s">
@@ -4140,7 +4166,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="68"/>
       <c r="B61" s="72"/>
       <c r="C61" s="5" t="s">
@@ -4154,7 +4180,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="68"/>
       <c r="B62" s="72"/>
       <c r="C62" s="5" t="s">
@@ -4168,7 +4194,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="68"/>
       <c r="B63" s="72"/>
       <c r="C63" s="5" t="s">
@@ -4182,7 +4208,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="68"/>
       <c r="B64" s="72"/>
       <c r="C64" s="5" t="s">
@@ -4196,12 +4222,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="68"/>
       <c r="B65" s="77"/>
       <c r="E65" s="10"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="68"/>
       <c r="B66" s="74" t="s">
         <v>6</v>
@@ -4217,7 +4243,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="68"/>
       <c r="B67" s="72"/>
       <c r="C67" s="5" t="s">
@@ -4231,7 +4257,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="68"/>
       <c r="B68" s="66"/>
       <c r="C68" s="5" t="s">
@@ -4245,7 +4271,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="68"/>
       <c r="B69" s="66"/>
       <c r="C69" s="5" t="s">
@@ -4259,7 +4285,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="68"/>
       <c r="B70" s="66"/>
       <c r="C70" s="5" t="s">
@@ -4273,7 +4299,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="68"/>
       <c r="B71" s="66"/>
       <c r="C71" s="5" t="s">
@@ -4287,7 +4313,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="68"/>
       <c r="B72" s="66"/>
       <c r="C72" s="5" t="s">
@@ -4301,7 +4327,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="68"/>
       <c r="B73" s="66"/>
       <c r="C73" s="5" t="s">
@@ -4315,7 +4341,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="68"/>
       <c r="B74" s="66"/>
       <c r="C74" s="5" t="s">
@@ -4329,7 +4355,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="68"/>
       <c r="B75" s="66"/>
       <c r="C75" s="5" t="s">
@@ -4343,7 +4369,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="68"/>
       <c r="B76" s="66"/>
       <c r="C76" s="5" t="s">
@@ -4357,7 +4383,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="73"/>
       <c r="B77" s="75"/>
       <c r="C77" s="18"/>
@@ -4365,7 +4391,7 @@
       <c r="E77" s="19"/>
       <c r="F77" s="18"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="67" t="s">
         <v>72</v>
       </c>
@@ -4383,7 +4409,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="68"/>
       <c r="B79" s="66"/>
       <c r="C79" s="5" t="s">
@@ -4397,7 +4423,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="68"/>
       <c r="B80" s="71"/>
       <c r="C80" s="14"/>
@@ -4405,7 +4431,7 @@
       <c r="E80" s="20"/>
       <c r="F80" s="14"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="68"/>
       <c r="B81" s="70" t="s">
         <v>337</v>
@@ -4421,7 +4447,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="68"/>
       <c r="B82" s="66"/>
       <c r="C82" s="5" t="s">
@@ -4435,7 +4461,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="68"/>
       <c r="B83" s="71"/>
       <c r="C83" s="14"/>
@@ -4443,7 +4469,7 @@
       <c r="E83" s="20"/>
       <c r="F83" s="14"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="68"/>
       <c r="B84" s="66" t="s">
         <v>379</v>
@@ -4459,7 +4485,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="68"/>
       <c r="B85" s="66"/>
       <c r="C85" s="5" t="s">
@@ -4473,12 +4499,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="68"/>
       <c r="B86" s="66"/>
       <c r="E86" s="8"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="68"/>
       <c r="B87" s="74" t="s">
         <v>4</v>
@@ -4494,7 +4520,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="68"/>
       <c r="B88" s="72"/>
       <c r="C88" s="5" t="s">
@@ -4508,7 +4534,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="68"/>
       <c r="B89" s="72"/>
       <c r="C89" s="5" t="s">
@@ -4522,7 +4548,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="68"/>
       <c r="B90" s="72"/>
       <c r="C90" s="5" t="s">
@@ -4536,7 +4562,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="68"/>
       <c r="B91" s="72"/>
       <c r="C91" s="5" t="s">
@@ -4550,7 +4576,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="68"/>
       <c r="B92" s="72"/>
       <c r="C92" s="5" t="s">
@@ -4564,7 +4590,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="68"/>
       <c r="B93" s="72"/>
       <c r="C93" s="5" t="s">
@@ -4578,7 +4604,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="68"/>
       <c r="B94" s="72"/>
       <c r="C94" s="5" t="s">
@@ -4592,7 +4618,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="68"/>
       <c r="B95" s="72"/>
       <c r="C95" s="5" t="s">
@@ -4606,11 +4632,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="68"/>
       <c r="B96" s="77"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="68"/>
       <c r="B97" s="74" t="s">
         <v>5</v>
@@ -4626,7 +4652,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="68"/>
       <c r="B98" s="72"/>
       <c r="C98" s="5" t="s">
@@ -4640,7 +4666,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="68"/>
       <c r="B99" s="72"/>
       <c r="C99" s="5" t="s">
@@ -4654,7 +4680,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="68"/>
       <c r="B100" s="72"/>
       <c r="C100" s="5" t="s">
@@ -4668,7 +4694,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="68"/>
       <c r="B101" s="72"/>
       <c r="C101" s="5" t="s">
@@ -4682,7 +4708,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="68"/>
       <c r="B102" s="72"/>
       <c r="C102" s="5" t="s">
@@ -4696,7 +4722,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="68"/>
       <c r="B103" s="72"/>
       <c r="C103" s="5" t="s">
@@ -4710,7 +4736,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="68"/>
       <c r="B104" s="72"/>
       <c r="C104" s="5" t="s">
@@ -4724,7 +4750,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="68"/>
       <c r="B105" s="72"/>
       <c r="C105" s="5" t="s">
@@ -4738,11 +4764,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="73"/>
       <c r="B106" s="78"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="67" t="s">
         <v>76</v>
       </c>
@@ -4760,7 +4786,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="68"/>
       <c r="B108" s="66"/>
       <c r="C108" s="5" t="s">
@@ -4774,7 +4800,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="68"/>
       <c r="B109" s="71"/>
       <c r="C109" s="14"/>
@@ -4782,7 +4808,7 @@
       <c r="E109" s="15"/>
       <c r="F109" s="14"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="68"/>
       <c r="B110" s="70" t="s">
         <v>299</v>
@@ -4798,7 +4824,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="68"/>
       <c r="B111" s="66"/>
       <c r="C111" s="5" t="s">
@@ -4812,12 +4838,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="68"/>
       <c r="B112" s="71"/>
       <c r="E112" s="10"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="68"/>
       <c r="B113" s="70" t="s">
         <v>79</v>
@@ -4833,7 +4859,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="68"/>
       <c r="B114" s="66"/>
       <c r="C114" s="5" t="s">
@@ -4847,7 +4873,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="68"/>
       <c r="B115" s="71"/>
       <c r="C115" s="14"/>
@@ -4855,7 +4881,7 @@
       <c r="E115" s="15"/>
       <c r="F115" s="14"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="68"/>
       <c r="B116" s="70" t="s">
         <v>258</v>
@@ -4871,7 +4897,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="68"/>
       <c r="B117" s="66"/>
       <c r="C117" s="5" t="s">
@@ -4885,7 +4911,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="73"/>
       <c r="B118" s="75"/>
       <c r="C118" s="18"/>
@@ -4893,7 +4919,7 @@
       <c r="E118" s="19"/>
       <c r="F118" s="18"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="67" t="s">
         <v>163</v>
       </c>
@@ -4911,7 +4937,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="68"/>
       <c r="B120" s="66"/>
       <c r="C120" s="5" t="s">
@@ -4924,7 +4950,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="68"/>
       <c r="B121" s="71"/>
       <c r="C121" s="14"/>
@@ -4932,7 +4958,7 @@
       <c r="E121" s="14"/>
       <c r="F121" s="14"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="68"/>
       <c r="B122" s="70" t="s">
         <v>183</v>
@@ -4947,7 +4973,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="68"/>
       <c r="B123" s="66"/>
       <c r="C123" s="5" t="s">
@@ -4960,7 +4986,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="68"/>
       <c r="B124" s="66"/>
       <c r="C124" s="5" t="s">
@@ -4973,7 +4999,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="68"/>
       <c r="B125" s="66"/>
       <c r="C125" s="5" t="s">
@@ -4986,7 +5012,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="68"/>
       <c r="B126" s="66"/>
       <c r="C126" s="5" t="s">
@@ -4999,7 +5025,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="68"/>
       <c r="B127" s="66"/>
       <c r="C127" s="5" t="s">
@@ -5012,11 +5038,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="68"/>
       <c r="B128" s="66"/>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="68"/>
       <c r="B129" s="70" t="s">
         <v>206</v>
@@ -5032,7 +5058,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="68"/>
       <c r="B130" s="66"/>
       <c r="C130" s="5" t="s">
@@ -5045,7 +5071,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="68"/>
       <c r="B131" s="66"/>
       <c r="C131" s="5" t="s">
@@ -5058,7 +5084,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="68"/>
       <c r="B132" s="66"/>
       <c r="C132" s="5" t="s">
@@ -5071,7 +5097,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="68"/>
       <c r="B133" s="66"/>
       <c r="C133" s="5" t="s">
@@ -5084,7 +5110,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="68"/>
       <c r="B134" s="66"/>
       <c r="C134" s="5" t="s">
@@ -5097,7 +5123,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="68"/>
       <c r="B135" s="66"/>
       <c r="C135" s="5" t="s">
@@ -5110,7 +5136,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="68"/>
       <c r="B136" s="66"/>
       <c r="C136" s="5" t="s">
@@ -5123,7 +5149,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="68"/>
       <c r="B137" s="66"/>
       <c r="C137" s="5" t="s">
@@ -5136,7 +5162,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="68"/>
       <c r="B138" s="66"/>
       <c r="C138" s="5" t="s">
@@ -5149,7 +5175,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="68"/>
       <c r="B139" s="66"/>
       <c r="C139" s="5" t="s">
@@ -5162,7 +5188,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="68"/>
       <c r="B140" s="66"/>
       <c r="C140" s="5" t="s">
@@ -5175,11 +5201,11 @@
         <v>213</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="68"/>
       <c r="B141" s="66"/>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="68"/>
       <c r="B142" s="70" t="s">
         <v>222</v>
@@ -5195,7 +5221,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" s="68"/>
       <c r="B143" s="66"/>
       <c r="C143" s="5" t="s">
@@ -5208,7 +5234,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" s="68"/>
       <c r="B144" s="66"/>
       <c r="C144" s="5" t="s">
@@ -5221,7 +5247,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" s="68"/>
       <c r="B145" s="66"/>
       <c r="C145" s="5" t="s">
@@ -5234,7 +5260,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="68"/>
       <c r="B146" s="66"/>
       <c r="C146" s="5" t="s">
@@ -5247,11 +5273,11 @@
         <v>213</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" s="68"/>
       <c r="B147" s="71"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" s="68"/>
       <c r="B148" s="70" t="s">
         <v>384</v>
@@ -5267,7 +5293,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" s="68"/>
       <c r="B149" s="66"/>
       <c r="C149" s="5" t="s">
